--- a/dados.xlsx
+++ b/dados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iastech.sharepoint.com/sites/Vendas/Documentos Compartilhados/General/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henri\Downloads\Henrique_daIASTECH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2416" documentId="8_{23619F0A-8DFA-4910-A6F1-9CA12DB1BCC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEC095F2-1DF0-45B5-B197-4C6F6125CFAF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58F6EDA-39C7-422A-B0C2-8F532D9884BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{9518D04A-E168-46DF-8442-C0FBA6A70E69}"/>
+    <workbookView xWindow="-28920" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{9518D04A-E168-46DF-8442-C0FBA6A70E69}"/>
   </bookViews>
   <sheets>
     <sheet name="ITENS" sheetId="2" r:id="rId1"/>
@@ -42,9 +42,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="305">
   <si>
-    <t>codigo</t>
-  </si>
-  <si>
     <t>QTD</t>
   </si>
   <si>
@@ -60,19 +57,7 @@
     <t>FABRICANTE</t>
   </si>
   <si>
-    <t>caixa original?</t>
-  </si>
-  <si>
-    <t>lacrado?</t>
-  </si>
-  <si>
     <t>ESTADO</t>
-  </si>
-  <si>
-    <t>Valor Anunciado</t>
-  </si>
-  <si>
-    <t>LINK MERCADO LIVRE</t>
   </si>
   <si>
     <t>1797-RPA</t>
@@ -994,6 +979,21 @@
   </si>
   <si>
     <t>leonardo.oliveira@iastech.com</t>
+  </si>
+  <si>
+    <t>CÓDIGO</t>
+  </si>
+  <si>
+    <t>CAIXA?</t>
+  </si>
+  <si>
+    <t>LACRE?</t>
+  </si>
+  <si>
+    <t>VALOR</t>
+  </si>
+  <si>
+    <t>ANUNCIO / CONTATO</t>
   </si>
 </sst>
 </file>
@@ -1275,9 +1275,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office 2013 - 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1315,7 +1315,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1421,7 +1421,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1563,7 +1563,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1572,2505 +1572,2505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDEB1426-66DA-4209-A518-57588F42F320}">
   <dimension ref="A1:K107"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="30.140625" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="11"/>
-    <col min="3" max="3" width="25.7109375" style="11" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" style="11" customWidth="1"/>
+    <col min="1" max="1" width="30.109375" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="11"/>
+    <col min="3" max="3" width="25.6640625" style="11" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" style="11" customWidth="1"/>
     <col min="5" max="5" width="27" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" style="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="13" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="136.85546875" customWidth="1"/>
+    <col min="9" max="9" width="14.88671875" style="13" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="136.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="I1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>8</v>
-      </c>
       <c r="J1" s="6" t="s">
-        <v>9</v>
+        <v>303</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>10</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B2" s="11">
         <v>1</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I2" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J2" s="8">
         <v>9500</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B3" s="11">
         <v>1</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J3" s="8">
         <v>4500</v>
       </c>
       <c r="K3" s="15" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B4" s="11">
         <v>1</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J4" s="8">
         <v>4500</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B5" s="11">
         <v>1</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J5" s="8">
         <v>800</v>
       </c>
       <c r="K5" s="15" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B6" s="11">
         <v>14</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J6" s="8">
         <v>2272.5</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B7" s="11">
         <v>1</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J7" s="8">
         <v>6000</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B8" s="11">
         <v>1</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J8" s="8">
         <v>21915</v>
       </c>
       <c r="K8" s="15" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B9" s="11">
         <v>5</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J9" s="8">
         <v>950</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B10" s="11">
         <v>5</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J10" s="8">
         <v>950</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B11" s="11">
         <v>1</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J11" s="8">
         <v>850</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B12" s="11">
         <v>1</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J12" s="8">
         <v>21500</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B13" s="11">
         <v>5</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J13" s="8">
         <v>950</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B14" s="11">
         <v>11</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J14" s="8">
         <v>1250</v>
       </c>
       <c r="K14" s="15" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B15" s="11">
         <v>1</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J15" s="8">
         <v>2550</v>
       </c>
       <c r="K15" s="15" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B16" s="11">
         <v>5</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J16" s="8">
         <v>900</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B17" s="11">
         <v>8</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J17" s="8">
         <v>1325</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B18" s="11">
         <v>2</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J18" s="8">
         <v>592.5</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B19" s="11">
         <v>4</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J19" s="8">
         <v>2500</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B20" s="11">
         <v>2</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J20" s="8">
         <v>900</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B21" s="11">
         <v>2</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J21" s="8">
         <v>2980</v>
       </c>
       <c r="K21" s="15" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B22" s="11">
         <v>3</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H22" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J22" s="8">
         <v>495</v>
       </c>
       <c r="K22" s="15" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B23" s="11">
         <v>4</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H23" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J23" s="8">
         <v>395</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B24" s="11">
         <v>1</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J24" s="8">
         <v>6900</v>
       </c>
       <c r="K24" s="15" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B25" s="11">
         <v>5</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H25" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J25" s="8">
         <v>420</v>
       </c>
       <c r="K25" s="15" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B26" s="11">
         <v>1</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G26" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J26" s="8">
         <v>945</v>
       </c>
       <c r="K26" s="15" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B27" s="11">
         <v>1</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J27" s="8">
         <v>6000</v>
       </c>
       <c r="K27" s="15" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B28" s="11">
         <v>1</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J28" s="8">
         <v>325</v>
       </c>
       <c r="K28" s="15" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B29" s="11">
         <v>2</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J29" s="8">
         <v>120</v>
       </c>
       <c r="K29" s="15" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B30" s="11">
         <v>1</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F30" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J30" s="8">
         <v>900</v>
       </c>
       <c r="K30" s="15" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B31" s="11">
         <v>1</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F31" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J31" s="8">
         <v>3650</v>
       </c>
       <c r="K31" s="15" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B32" s="11">
         <v>1</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F32" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I32" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J32" s="8">
         <v>2950</v>
       </c>
       <c r="K32" s="15" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B33" s="11">
         <v>3</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I33" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J33" s="8">
         <v>4100</v>
       </c>
       <c r="K33" s="15" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:11">
       <c r="A34" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B34" s="11">
         <v>1</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I34" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J34" s="8">
         <v>1396</v>
       </c>
       <c r="K34" s="15" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B35" s="11">
         <v>5</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I35" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J35" s="8">
         <v>705</v>
       </c>
       <c r="K35" s="15" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:11">
       <c r="A36" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B36" s="11">
         <v>3</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I36" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J36" s="8">
         <v>15500</v>
       </c>
       <c r="K36" s="15" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="17.25" customHeight="1">
       <c r="A37" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B37" s="11">
         <v>1</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F37" s="11" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I37" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J37" s="8">
         <v>705</v>
       </c>
       <c r="K37" s="15" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B38" s="11">
         <v>1</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F38" s="11" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I38" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J38" s="8">
         <v>545</v>
       </c>
       <c r="K38" s="15" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:11">
       <c r="A39" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B39" s="11">
         <v>1</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I39" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J39" s="8">
         <v>8205</v>
       </c>
       <c r="K39" s="15" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:11">
       <c r="A40" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B40" s="11">
         <v>1</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F40" s="11" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I40" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J40" s="8">
         <v>7500</v>
       </c>
       <c r="K40" s="15" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B41" s="11">
         <v>5</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F41" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I41" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J41" s="8">
         <v>9750</v>
       </c>
       <c r="K41" s="15" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B42" s="11">
         <v>1</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F42" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I42" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J42" s="8">
         <v>4650</v>
       </c>
       <c r="K42" s="15" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B43" s="11">
         <v>1</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F43" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I43" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J43" s="8">
         <v>1980</v>
       </c>
       <c r="K43" s="15" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B44" s="11">
         <v>2</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F44" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I44" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J44" s="8">
         <v>255</v>
       </c>
       <c r="K44" s="15" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B45" s="11">
         <v>2</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F45" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I45" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J45" s="8">
         <v>1650</v>
       </c>
       <c r="K45" s="15" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B46" s="11">
         <v>4</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F46" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I46" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J46" s="8">
         <v>3999</v>
       </c>
       <c r="K46" s="15" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B47" s="11">
         <v>1</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F47" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I47" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J47" s="8">
         <v>3999</v>
       </c>
       <c r="K47" s="15" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" spans="1:11">
       <c r="A48" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B48" s="11">
         <v>1</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F48" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I48" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J48" s="8">
         <v>6500</v>
       </c>
       <c r="K48" s="15" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="B49" s="11">
         <v>6</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F49" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I49" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J49" s="8">
         <v>346.5</v>
       </c>
       <c r="K49" s="15" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B50" s="11">
         <v>1</v>
       </c>
       <c r="C50" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D50" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="D50" s="11" t="s">
-        <v>130</v>
-      </c>
       <c r="E50" s="11" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F50" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I50" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J50" s="8">
         <v>346.5</v>
       </c>
       <c r="K50" s="15" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B51" s="11">
         <v>6</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="F51" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I51" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J51" s="8">
         <v>980</v>
       </c>
       <c r="K51" s="15" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B52" s="11">
         <v>5</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F52" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I52" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J52" s="8">
         <v>999</v>
       </c>
       <c r="K52" s="15" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B53" s="11">
         <v>16</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F53" s="11" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I53" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J53" s="8">
         <v>300</v>
       </c>
       <c r="K53" s="15" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B54" s="11">
         <v>1</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="F54" s="11" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I54" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J54" s="8">
         <v>1500</v>
       </c>
       <c r="K54" s="15" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="55" spans="1:11">
       <c r="A55" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B55" s="11">
         <v>48</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I55" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J55" s="8">
         <v>2100</v>
       </c>
       <c r="K55" s="15" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B56" s="11">
         <v>5</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I56" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J56" s="8">
         <v>240</v>
       </c>
       <c r="K56" s="15" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="57" spans="1:11">
       <c r="A57" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B57" s="11">
         <f>2 - 1</f>
         <v>1</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I57" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J57" s="8">
         <v>350</v>
       </c>
       <c r="K57" s="15" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B58" s="11">
         <v>1</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I58" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J58" s="8">
         <v>4480</v>
       </c>
       <c r="K58" s="15" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B59" s="11">
         <v>8</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I59" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J59" s="8">
         <v>850</v>
       </c>
       <c r="K59" s="15" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B60" s="11">
         <v>10</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D60" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="E60" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="E60" s="11" t="s">
-        <v>168</v>
-      </c>
       <c r="F60" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I60" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J60" s="8">
         <v>125</v>
       </c>
       <c r="K60" s="15" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B61" s="11">
         <v>1</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I61" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J61" s="8">
         <v>400</v>
       </c>
       <c r="K61" s="15" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B62" s="11">
         <v>1</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I62" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J62" s="8">
         <v>650</v>
       </c>
       <c r="K62" s="15" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B63" s="11">
         <v>1</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G63" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I63" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J63" s="8">
         <v>300</v>
       </c>
       <c r="K63" s="15" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B64" s="11">
         <v>1</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G64" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I64" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J64" s="8">
         <v>2380</v>
       </c>
       <c r="K64" s="15" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B65" s="11">
         <v>3</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H65" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I65" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J65" s="8">
         <v>500</v>
       </c>
       <c r="K65" s="15" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B66" s="11">
         <v>3</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="G66" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J66" s="8">
         <v>600</v>
       </c>
       <c r="K66" s="15" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="67" spans="1:11">
       <c r="A67" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B67" s="11">
         <v>1</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F67" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G67" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H67" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I67" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J67" s="8">
         <v>138</v>
       </c>
       <c r="K67" s="15" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B68" s="11">
         <v>1</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="F68" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I68" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J68" s="8">
         <v>260</v>
       </c>
       <c r="K68" s="15" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B69" s="11">
         <v>2</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F69" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H69" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I69" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J69" s="8">
         <v>780</v>
       </c>
       <c r="K69" s="15" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="70" spans="1:11">
       <c r="A70" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B70" s="11">
         <v>2</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="F70" s="11" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="G70" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H70" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I70" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J70" s="8">
         <v>1300</v>
       </c>
       <c r="K70" s="15" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="71" spans="1:11">
       <c r="A71" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B71" s="11">
         <v>1</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F71" s="11" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G71" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H71" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I71" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J71" s="8">
         <v>2800</v>
       </c>
       <c r="K71" s="16" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -4081,381 +4081,381 @@
         <v>5</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F72" s="11" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="G72" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H72" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I72" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J72" s="8">
         <v>50</v>
       </c>
       <c r="K72" s="15" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="73" spans="1:11">
       <c r="A73" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="B73" s="11">
         <v>1</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="F73" s="11" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I73" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J73" s="8">
         <v>1800</v>
       </c>
       <c r="K73" s="15" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="9" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="B74" s="11">
         <v>10</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F74" s="11" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="G74" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H74" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I74" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J74" s="10">
         <v>75</v>
       </c>
       <c r="K74" s="15" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B75" s="11">
         <v>1</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F75" s="11" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="G75" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H75" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I75" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J75" s="8">
         <v>60</v>
       </c>
       <c r="K75" s="15" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="B76" s="11">
         <v>1</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="F76" s="11" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G76" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H76" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I76" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J76" s="8">
         <v>12</v>
       </c>
       <c r="K76" s="15" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B77" s="11">
         <v>50</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F77" s="11" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="G77" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H77" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I77" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J77" s="8">
         <v>40</v>
       </c>
       <c r="K77" s="15" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="78" spans="1:11">
       <c r="A78" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B78" s="11">
         <v>2</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E78" s="11" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F78" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G78" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H78" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I78" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J78" s="8">
         <v>6100</v>
       </c>
       <c r="K78" s="15" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B79" s="11">
         <v>1</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E79" s="11" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F79" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G79" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H79" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I79" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J79" s="8">
         <v>3400</v>
       </c>
       <c r="K79" s="15" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B80" s="11">
         <v>1</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F80" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G80" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H80" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I80" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J80" s="8">
         <v>7300</v>
       </c>
       <c r="K80" s="15" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B81" s="11">
         <v>1</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E81" s="11" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F81" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G81" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H81" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I81" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J81" s="8">
         <v>1130</v>
       </c>
       <c r="K81" s="15" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="82" spans="1:11">
       <c r="A82" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B82" s="11">
         <v>1</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F82" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G82" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H82" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I82" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J82" s="8">
         <v>910</v>
       </c>
       <c r="K82" s="15" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -4466,31 +4466,31 @@
         <v>4</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E83" s="11" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F83" s="11" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="G83" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H83" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I83" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J83" s="8">
         <v>520</v>
       </c>
       <c r="K83" s="15" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -4501,836 +4501,836 @@
         <v>8</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E84" s="11" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F84" s="11" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="G84" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H84" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I84" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J84" s="8">
         <v>205</v>
       </c>
       <c r="K84" s="15" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="85" spans="1:11">
       <c r="A85" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B85" s="11">
         <v>697</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E85" s="11" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="F85" s="11" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="G85" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H85" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I85" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J85" s="8">
         <v>99.9</v>
       </c>
       <c r="K85" s="15" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
     <row r="86" spans="1:11">
       <c r="A86" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B86" s="11">
         <v>12</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E86" s="11" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F86" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G86" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H86" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I86" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J86" s="8">
         <v>2950</v>
       </c>
       <c r="K86" s="15" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="87" spans="1:11">
       <c r="A87" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B87" s="11">
         <v>2</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E87" s="11" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F87" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G87" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H87" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I87" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J87" s="8">
         <v>700</v>
       </c>
       <c r="K87" s="15" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
     </row>
     <row r="88" spans="1:11">
       <c r="A88" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B88" s="11">
         <v>2</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F88" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G88" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H88" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I88" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J88" s="8">
         <v>720</v>
       </c>
       <c r="K88" s="15" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B89" s="11">
         <v>1</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E89" s="11" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F89" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G89" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H89" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I89" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J89" s="8">
         <v>2800</v>
       </c>
       <c r="K89" s="15" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B90" s="11">
         <v>1</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E90" s="11" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F90" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G90" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H90" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I90" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J90" s="8">
         <v>3490</v>
       </c>
       <c r="K90" s="15" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B91" s="11">
         <v>1</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E91" s="11" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F91" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G91" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H91" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I91" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J91" s="8">
         <v>3688</v>
       </c>
       <c r="K91" s="15" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="92" spans="1:11">
       <c r="A92" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B92" s="11">
         <v>1</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E92" s="11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F92" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G92" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H92" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I92" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J92" s="8">
         <v>5200</v>
       </c>
       <c r="K92" s="15" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="93" spans="1:11">
       <c r="A93" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B93" s="11">
         <v>1</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E93" s="11" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F93" s="11" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G93" s="11" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H93" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I93" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J93" s="8">
         <v>295</v>
       </c>
       <c r="K93" s="15" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
     </row>
     <row r="94" spans="1:11">
       <c r="A94" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B94" s="11">
         <v>1</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E94" s="11" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F94" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G94" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H94" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I94" s="13" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J94" s="7">
         <v>520</v>
       </c>
       <c r="K94" s="15" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
     </row>
     <row r="95" spans="1:11">
       <c r="A95" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B95" s="11">
         <v>1</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E95" s="11" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F95" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G95" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H95" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I95" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J95" s="7">
         <v>1200</v>
       </c>
       <c r="K95" s="15" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
     </row>
     <row r="96" spans="1:11">
       <c r="A96" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B96" s="11">
         <v>1</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E96" s="11" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F96" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G96" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H96" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I96" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J96" s="7">
         <v>1900</v>
       </c>
       <c r="K96" s="15" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="97" spans="1:11">
       <c r="A97" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B97" s="11">
         <v>1</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E97" s="11" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F97" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G97" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H97" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I97" s="13" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J97" s="7">
         <v>3000</v>
       </c>
       <c r="K97" s="15" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B98" s="11">
         <v>1</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E98" s="11" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F98" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G98" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H98" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I98" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J98" s="7">
         <v>500</v>
       </c>
       <c r="K98" s="15" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="99" spans="1:11">
       <c r="A99" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B99" s="11">
         <v>1</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E99" s="11" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F99" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G99" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H99" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I99" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J99" s="7">
         <v>2500</v>
       </c>
       <c r="K99" s="15" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="100" spans="1:11">
       <c r="A100" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B100" s="11">
         <v>4</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E100" s="11" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F100" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G100" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H100" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I100" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J100" s="7">
         <v>160</v>
       </c>
       <c r="K100" s="15" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="101" spans="1:11">
       <c r="A101" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B101" s="11">
         <v>4</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E101" s="11" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F101" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G101" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H101" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I101" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J101" s="7">
         <v>99</v>
       </c>
       <c r="K101" s="15" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="102" spans="1:11">
       <c r="A102" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B102" s="11">
         <v>1</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E102" s="11" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="F102" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G102" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H102" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I102" s="13" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J102" s="8">
         <v>5000</v>
       </c>
       <c r="K102" s="15" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="103" spans="1:11">
       <c r="A103" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B103" s="11">
         <v>1</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E103" s="11" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="F103" s="11" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G103" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H103" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I103" s="13" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J103" s="7">
         <v>899</v>
       </c>
       <c r="K103" s="15" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="104" spans="1:11">
       <c r="A104" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B104" s="11">
         <v>1</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E104" s="11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F104" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G104" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H104" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I104" s="13" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J104" s="7">
         <v>3000</v>
       </c>
       <c r="K104" s="15" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="105" spans="1:11">
       <c r="A105" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B105" s="11">
         <v>1</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E105" s="11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F105" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G105" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H105" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I105" s="13" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J105" s="7">
         <v>1950</v>
       </c>
       <c r="K105" s="15" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="106" spans="1:11">
       <c r="A106" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B106" s="11">
         <v>1</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D106" s="11" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="E106" s="11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F106" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G106" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H106" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I106" s="13" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J106" s="7">
         <v>375</v>
       </c>
       <c r="K106" s="15" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
     </row>
     <row r="107" spans="1:11">
       <c r="A107" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B107" s="11">
         <v>1</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D107" s="11" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="E107" s="11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F107" s="11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G107" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H107" s="11" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I107" s="13" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J107" s="8">
         <v>650</v>
       </c>
       <c r="K107" s="15" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -5457,24 +5457,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9081623D-7020-4499-A7BD-D7B5650988D7}">
   <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="64.7109375" customWidth="1"/>
+    <col min="1" max="1" width="64.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="48">
       <c r="A1" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="36">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="34.799999999999997">
       <c r="A2" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="48">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="46.2">
       <c r="A3" s="2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -5485,25 +5485,25 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="24">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="22.8">
       <c r="A8" s="5" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5"/>
     </row>
-    <row r="10" spans="1:5" ht="24">
+    <row r="10" spans="1:5" ht="22.8">
       <c r="A10" s="5" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="36">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="34.200000000000003">
       <c r="A11" s="5" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -5514,7 +5514,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="17" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
@@ -5523,7 +5523,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="20" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B15" s="21"/>
       <c r="C15" s="21"/>
@@ -5532,7 +5532,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="23" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B16" s="24"/>
       <c r="C16" s="24"/>
@@ -5561,12 +5561,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5210180e-56dd-4f8d-b0dc-75c44b0b75d4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="678196fe-e6fd-4f63-b0bf-af539c375111" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5765,24 +5767,48 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5210180e-56dd-4f8d-b0dc-75c44b0b75d4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="678196fe-e6fd-4f63-b0bf-af539c375111" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99923289-A4A6-484C-9EE5-0B486CC2CB2A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8DD6199-78B9-45EB-BE35-B65B9866F916}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5210180e-56dd-4f8d-b0dc-75c44b0b75d4"/>
+    <ds:schemaRef ds:uri="678196fe-e6fd-4f63-b0bf-af539c375111"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{115536AB-D72A-489D-A83E-7207B399A9DE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{115536AB-D72A-489D-A83E-7207B399A9DE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="5210180e-56dd-4f8d-b0dc-75c44b0b75d4"/>
+    <ds:schemaRef ds:uri="678196fe-e6fd-4f63-b0bf-af539c375111"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8DD6199-78B9-45EB-BE35-B65B9866F916}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99923289-A4A6-484C-9EE5-0B486CC2CB2A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>